--- a/Result/profitability/6194.xlsx
+++ b/Result/profitability/6194.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.74</v>
+        <v>0.6387499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>15.39875</v>
+        <v>13.95375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8225</v>
+        <v>0.61</v>
       </c>
       <c r="N3" t="n">
-        <v>16.03625</v>
+        <v>14.0475</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>0.80875</v>
+        <v>0.6575</v>
       </c>
       <c r="N4" t="n">
-        <v>15.93</v>
+        <v>13.945</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66</v>
+        <v>0.615</v>
       </c>
       <c r="N5" t="n">
-        <v>14.635</v>
+        <v>12.99875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7075</v>
+        <v>0.5875</v>
       </c>
       <c r="N6" t="n">
-        <v>14.3375</v>
+        <v>12.96125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.97</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7375</v>
+        <v>0.665</v>
       </c>
       <c r="N7" t="n">
-        <v>16.14375</v>
+        <v>15.12875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.885</v>
+        <v>0.8150000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>18.32125</v>
+        <v>17.06</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8150000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>19.49375</v>
@@ -1772,7 +1772,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7462500000000001</v>
+        <v>0.74625</v>
       </c>
       <c r="N11" t="n">
         <v>20.05375</v>
@@ -1899,7 +1899,7 @@
         <v>0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0.62</v>
+        <v>0.6199999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>20.39125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6194</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>224</v>
+      </c>
+      <c r="D75" t="n">
+        <v>219</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.0475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.696969696969697</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.8117457763475463</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.769230769230769</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8483473752430331</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
